--- a/ksoft_old/docs/records/Item_Family_Commercial_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Family_Commercial_Records.xlsx
@@ -1774,13 +1774,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C05C0A5-4F9A-47EE-990B-59CC70DE8886}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8586D1E0-E8EA-4CBC-B8BB-71BBD5F73197}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8857C73A-071D-466C-A287-00E58CE82405}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C38FAF09-B3BA-41D3-B5DA-C9F0FB6556C1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE91A59-F3D1-498D-8B5F-57FDFBD23F71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67821E29-883C-4F33-ABDE-2B004F7F2F6A}"/>
 </file>
--- a/ksoft_old/docs/records/Item_Family_Commercial_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Family_Commercial_Records.xlsx
@@ -1774,13 +1774,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8586D1E0-E8EA-4CBC-B8BB-71BBD5F73197}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EEF810F-F473-46FF-9C99-98F66392B765}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C38FAF09-B3BA-41D3-B5DA-C9F0FB6556C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{904B660A-344F-4E40-8924-09F060920039}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67821E29-883C-4F33-ABDE-2B004F7F2F6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D36945-FDE9-4D86-B84A-C5B49461AD3E}"/>
 </file>
--- a/ksoft_old/docs/records/Item_Family_Commercial_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Family_Commercial_Records.xlsx
@@ -1774,13 +1774,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EEF810F-F473-46FF-9C99-98F66392B765}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C05C0A5-4F9A-47EE-990B-59CC70DE8886}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{904B660A-344F-4E40-8924-09F060920039}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8857C73A-071D-466C-A287-00E58CE82405}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D36945-FDE9-4D86-B84A-C5B49461AD3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE91A59-F3D1-498D-8B5F-57FDFBD23F71}"/>
 </file>